--- a/backend/scripts/audit-output/expeditor-smoke/ex-5.1.8.xlsx
+++ b/backend/scripts/audit-output/expeditor-smoke/ex-5.1.8.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
-  <si>
-    <t>Загрузочный лист 5.1.8 (Время печати: 27.05.2026 19:51:41)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <si>
+    <t>Загрузочный лист 5.1.8 (Время печати: 28.05.2026 17:37:20)</t>
   </si>
   <si>
     <t>Дата заявки: 25.05.2026</t>
@@ -603,8 +603,8 @@
     <pageSetUpPr fitToPage="1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AD52"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <dimension ref="A1:AN52"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -614,7 +614,7 @@
     <col min="6" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -625,7 +625,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -638,7 +638,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -651,7 +651,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -664,7 +664,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -677,7 +677,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -690,7 +690,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
@@ -699,7 +699,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1407,6 +1407,6 @@
     <mergeCell ref="C52:D52"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>